--- a/360MasterData_AR.xlsx
+++ b/360MasterData_AR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0440AA8A-1D6E-4675-9785-1FD9BC7F3F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E0A2284-8C03-4B75-A1FE-5E0A8A6DA099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2653" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2653" uniqueCount="370">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -1045,9 +1045,6 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/HS-HYP-01.svg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/WelcomeVC.mp3</t>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/HS1-4.mp3</t>
@@ -2758,7 +2755,7 @@
     </row>
     <row r="2" spans="1:28" ht="18.3" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>27</v>
@@ -2770,7 +2767,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F2" s="38" t="s">
         <v>175</v>
@@ -2785,7 +2782,7 @@
         <v>1</v>
       </c>
       <c r="J2" s="61" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="K2" s="61" t="s">
         <v>160</v>
@@ -2833,7 +2830,7 @@
         <v>1</v>
       </c>
       <c r="Z2" s="67" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AA2" s="12">
         <v>45750</v>
@@ -2844,7 +2841,7 @@
     </row>
     <row r="3" spans="1:28" ht="20.25" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>27</v>
@@ -2856,7 +2853,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F3" s="38" t="s">
         <v>166</v>
@@ -2919,7 +2916,7 @@
         <v>1</v>
       </c>
       <c r="Z3" s="75" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AA3" s="12">
         <v>45750</v>
@@ -2930,7 +2927,7 @@
     </row>
     <row r="4" spans="1:28" ht="20.25" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>27</v>
@@ -2942,7 +2939,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F4" s="38" t="s">
         <v>165</v>
@@ -3011,7 +3008,7 @@
     </row>
     <row r="5" spans="1:28" ht="20.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>27</v>
@@ -3023,7 +3020,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F5" s="38" t="s">
         <v>163</v>
@@ -3093,7 +3090,7 @@
     </row>
     <row r="6" spans="1:28" ht="20.25" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>27</v>
@@ -3105,7 +3102,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F6" s="38" t="s">
         <v>164</v>
@@ -3175,7 +3172,7 @@
     </row>
     <row r="7" spans="1:28" ht="20.25" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>50</v>
@@ -3187,7 +3184,7 @@
         <v>7</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F7" s="38" t="s">
         <v>167</v>
@@ -3202,7 +3199,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="16" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>53</v>
@@ -3257,7 +3254,7 @@
     </row>
     <row r="8" spans="1:28" ht="20.25" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>50</v>
@@ -3269,7 +3266,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F8" s="38" t="s">
         <v>188</v>
@@ -3284,7 +3281,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="16" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>31</v>
@@ -3341,7 +3338,7 @@
     </row>
     <row r="9" spans="1:28" ht="20.25" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>50</v>
@@ -3353,7 +3350,7 @@
         <v>8</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F9" s="38" t="s">
         <v>162</v>
@@ -3368,7 +3365,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>61</v>
@@ -3425,7 +3422,7 @@
     </row>
     <row r="10" spans="1:28" ht="20.25" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>50</v>
@@ -3437,7 +3434,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F10" s="38" t="s">
         <v>208</v>
@@ -3509,7 +3506,7 @@
     </row>
     <row r="11" spans="1:28" ht="20.25" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>50</v>
@@ -3521,7 +3518,7 @@
         <v>10</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F11" s="38" t="s">
         <v>207</v>
@@ -3591,7 +3588,7 @@
     </row>
     <row r="12" spans="1:28" ht="20.25" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>50</v>
@@ -3603,7 +3600,7 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>168</v>
@@ -3675,7 +3672,7 @@
     </row>
     <row r="13" spans="1:28" ht="20.25" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>76</v>
@@ -3687,7 +3684,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>169</v>
@@ -3759,7 +3756,7 @@
     </row>
     <row r="14" spans="1:28" ht="20.25" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>76</v>
@@ -3771,7 +3768,7 @@
         <v>13</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>170</v>
@@ -3843,7 +3840,7 @@
     </row>
     <row r="15" spans="1:28" ht="20.25" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>76</v>
@@ -3855,7 +3852,7 @@
         <v>14</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F15" s="38" t="s">
         <v>171</v>
@@ -3927,7 +3924,7 @@
     </row>
     <row r="16" spans="1:28" ht="20.25" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>27</v>
@@ -3939,7 +3936,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>172</v>
@@ -4011,7 +4008,7 @@
     </row>
     <row r="17" spans="1:28" ht="20.25" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>27</v>
@@ -4023,7 +4020,7 @@
         <v>16</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F17" s="38" t="s">
         <v>173</v>
@@ -4095,7 +4092,7 @@
     </row>
     <row r="18" spans="1:28" ht="20.25" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>27</v>
@@ -4107,7 +4104,7 @@
         <v>17</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F18" s="38" t="s">
         <v>174</v>
@@ -4179,7 +4176,7 @@
     </row>
     <row r="19" spans="1:28" ht="20.25" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>97</v>
@@ -4191,7 +4188,7 @@
         <v>18</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F19" s="38" t="s">
         <v>176</v>
@@ -4206,7 +4203,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="16" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="K19" s="5" t="s">
         <v>99</v>
@@ -4263,7 +4260,7 @@
     </row>
     <row r="20" spans="1:28" ht="20.25" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>97</v>
@@ -4275,7 +4272,7 @@
         <v>19</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F20" s="38" t="s">
         <v>177</v>
@@ -4290,7 +4287,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="16" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>31</v>
@@ -4347,7 +4344,7 @@
     </row>
     <row r="21" spans="1:28" ht="20.25" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>97</v>
@@ -4359,7 +4356,7 @@
         <v>20</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F21" s="38" t="s">
         <v>178</v>
@@ -4431,7 +4428,7 @@
     </row>
     <row r="22" spans="1:28" ht="20.25" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>97</v>
@@ -4443,7 +4440,7 @@
         <v>21</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F22" s="38" t="s">
         <v>179</v>
@@ -4515,7 +4512,7 @@
     </row>
     <row r="23" spans="1:28" ht="20.25" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>97</v>
@@ -4527,7 +4524,7 @@
         <v>22</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F23" s="38" t="s">
         <v>180</v>
@@ -4601,7 +4598,7 @@
     </row>
     <row r="24" spans="1:28" ht="12" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>97</v>
@@ -4613,7 +4610,7 @@
         <v>23</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F24" s="38" t="s">
         <v>194</v>
@@ -4685,7 +4682,7 @@
     </row>
     <row r="25" spans="1:28" ht="12" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>97</v>
@@ -4697,7 +4694,7 @@
         <v>24</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F25" s="38" t="s">
         <v>189</v>
@@ -4769,7 +4766,7 @@
     </row>
     <row r="26" spans="1:28" ht="12" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>97</v>
@@ -4781,7 +4778,7 @@
         <v>25</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F26" s="38" t="s">
         <v>181</v>
@@ -4853,7 +4850,7 @@
     </row>
     <row r="27" spans="1:28" ht="12" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>97</v>
@@ -4865,7 +4862,7 @@
         <v>26</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F27" s="38" t="s">
         <v>190</v>
@@ -4937,7 +4934,7 @@
     </row>
     <row r="28" spans="1:28" ht="12" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>97</v>
@@ -4949,7 +4946,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F28" s="38" t="s">
         <v>191</v>
@@ -5021,7 +5018,7 @@
     </row>
     <row r="29" spans="1:28" ht="12" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>97</v>
@@ -5033,7 +5030,7 @@
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F29" s="38" t="s">
         <v>192</v>
@@ -5105,7 +5102,7 @@
     </row>
     <row r="30" spans="1:28" ht="12" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>97</v>
@@ -5117,7 +5114,7 @@
         <v>29</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F30" s="38" t="s">
         <v>193</v>
@@ -5189,7 +5186,7 @@
     </row>
     <row r="31" spans="1:28" ht="12" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>97</v>
@@ -5201,7 +5198,7 @@
         <v>30</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F31" s="38" t="s">
         <v>195</v>
@@ -5273,7 +5270,7 @@
     </row>
     <row r="32" spans="1:28" ht="12" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>97</v>
@@ -5285,7 +5282,7 @@
         <v>31</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F32" s="38" t="s">
         <v>196</v>
@@ -10396,7 +10393,7 @@
       </c>
       <c r="N3" s="35"/>
       <c r="O3" s="56" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q3"/>
     </row>
@@ -23014,13 +23011,13 @@
         <v>291</v>
       </c>
       <c r="D2" s="44" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E2" s="41" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F2" s="76" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G2" s="45" t="s">
         <v>146</v>
@@ -23032,7 +23029,7 @@
         <v>160</v>
       </c>
       <c r="J2" s="45" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K2" s="56" t="s">
         <v>266</v>
@@ -23049,13 +23046,13 @@
         <v>292</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E3" s="40" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F3" s="76" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G3" s="40" t="s">
         <v>147</v>
@@ -23067,7 +23064,7 @@
         <v>31</v>
       </c>
       <c r="J3" s="45" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K3" s="56" t="s">
         <v>266</v>
@@ -23084,13 +23081,13 @@
         <v>294</v>
       </c>
       <c r="D4" s="48" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E4" s="40" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F4" s="76" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G4" s="43" t="s">
         <v>146</v>
@@ -23102,7 +23099,7 @@
         <v>31</v>
       </c>
       <c r="J4" s="45" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K4" s="56" t="s">
         <v>266</v>
@@ -23119,13 +23116,13 @@
         <v>295</v>
       </c>
       <c r="D5" s="48" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E5" s="40" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F5" s="76" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G5" s="49" t="s">
         <v>146</v>
@@ -23154,13 +23151,13 @@
         <v>295</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E6" s="41" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G6" s="43" t="s">
         <v>146</v>
@@ -23172,7 +23169,7 @@
         <v>31</v>
       </c>
       <c r="J6" s="45" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K6" s="56" t="s">
         <v>266</v>
@@ -23189,13 +23186,13 @@
         <v>295</v>
       </c>
       <c r="D7" s="48" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E7" s="40" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F7" s="76" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G7" s="49" t="s">
         <v>146</v>
@@ -23224,13 +23221,13 @@
         <v>295</v>
       </c>
       <c r="D8" s="48" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E8" s="41" t="s">
+        <v>323</v>
+      </c>
+      <c r="F8" s="76" t="s">
         <v>324</v>
-      </c>
-      <c r="F8" s="76" t="s">
-        <v>325</v>
       </c>
       <c r="G8" s="41" t="s">
         <v>147</v>
@@ -23242,7 +23239,7 @@
         <v>31</v>
       </c>
       <c r="J8" s="41" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K8" s="56" t="s">
         <v>266</v>
@@ -23260,10 +23257,10 @@
       </c>
       <c r="D9" s="47"/>
       <c r="E9" s="40" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F9" s="76" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G9" s="49" t="s">
         <v>146</v>
@@ -23275,7 +23272,7 @@
         <v>31</v>
       </c>
       <c r="J9" s="51" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="K9" s="56" t="s">
         <v>266</v>
@@ -23293,10 +23290,10 @@
       </c>
       <c r="D10" s="44"/>
       <c r="E10" s="41" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F10" s="76" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G10" s="43" t="s">
         <v>146</v>
@@ -23308,7 +23305,7 @@
         <v>31</v>
       </c>
       <c r="J10" s="45" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K10" s="56" t="s">
         <v>266</v>
@@ -23326,10 +23323,10 @@
       </c>
       <c r="D11" s="47"/>
       <c r="E11" s="40" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F11" s="76" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G11" s="49" t="s">
         <v>146</v>
@@ -23341,7 +23338,7 @@
         <v>31</v>
       </c>
       <c r="J11" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K11" s="56" t="s">
         <v>266</v>
@@ -23359,10 +23356,10 @@
       </c>
       <c r="D12" s="44"/>
       <c r="E12" s="41" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F12" s="76" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G12" s="43" t="s">
         <v>146</v>
@@ -23374,7 +23371,7 @@
         <v>31</v>
       </c>
       <c r="J12" s="51" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K12" s="56" t="s">
         <v>266</v>
@@ -23392,10 +23389,10 @@
       </c>
       <c r="D13" s="47"/>
       <c r="E13" s="40" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F13" s="76" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G13" s="40" t="s">
         <v>147</v>
@@ -23407,7 +23404,7 @@
         <v>31</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K13" s="56" t="s">
         <v>266</v>
@@ -23425,10 +23422,10 @@
       </c>
       <c r="D14" s="44"/>
       <c r="E14" s="41" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F14" s="76" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G14" s="43" t="s">
         <v>146</v>
@@ -23440,7 +23437,7 @@
         <v>31</v>
       </c>
       <c r="J14" s="51" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="K14" s="56" t="s">
         <v>266</v>
@@ -23458,10 +23455,10 @@
       </c>
       <c r="D15" s="47"/>
       <c r="E15" s="40" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F15" s="76" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G15" s="49" t="s">
         <v>146</v>
@@ -23473,7 +23470,7 @@
         <v>31</v>
       </c>
       <c r="J15" s="45" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K15" s="56" t="s">
         <v>266</v>
@@ -23491,10 +23488,10 @@
       </c>
       <c r="D16" s="44"/>
       <c r="E16" s="41" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F16" s="76" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G16" s="43" t="s">
         <v>146</v>
@@ -23506,7 +23503,7 @@
         <v>31</v>
       </c>
       <c r="J16" s="45" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K16" s="56" t="s">
         <v>266</v>
@@ -23526,10 +23523,10 @@
         <v>149</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F17" s="76" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G17" s="49" t="s">
         <v>146</v>
@@ -23541,7 +23538,7 @@
         <v>31</v>
       </c>
       <c r="J17" s="45" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K17" s="56" t="s">
         <v>266</v>
@@ -23561,10 +23558,10 @@
         <v>150</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F18" s="76" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G18" s="41" t="s">
         <v>147</v>
@@ -23594,10 +23591,10 @@
       </c>
       <c r="D19" s="47"/>
       <c r="E19" s="40" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F19" s="76" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G19" s="49" t="s">
         <v>146</v>
@@ -23609,7 +23606,7 @@
         <v>31</v>
       </c>
       <c r="J19" s="45" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K19" s="56" t="s">
         <v>266</v>
@@ -23627,10 +23624,10 @@
       </c>
       <c r="D20" s="44"/>
       <c r="E20" s="41" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F20" s="76" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G20" s="43" t="s">
         <v>146</v>
@@ -23642,7 +23639,7 @@
         <v>31</v>
       </c>
       <c r="J20" s="45" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K20" s="56" t="s">
         <v>266</v>
@@ -23662,10 +23659,10 @@
         <v>148</v>
       </c>
       <c r="E21" s="40" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F21" s="76" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G21" s="49" t="s">
         <v>146</v>
@@ -23677,7 +23674,7 @@
         <v>31</v>
       </c>
       <c r="J21" s="45" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K21" s="56" t="s">
         <v>233</v>
@@ -23789,10 +23786,10 @@
         <v>240</v>
       </c>
       <c r="E2" s="67" t="s">
+        <v>315</v>
+      </c>
+      <c r="F2" s="69" t="s">
         <v>316</v>
-      </c>
-      <c r="F2" s="69" t="s">
-        <v>317</v>
       </c>
       <c r="G2" s="69" t="s">
         <v>250</v>
@@ -23814,13 +23811,13 @@
         <v>245</v>
       </c>
       <c r="E3" s="67" t="s">
+        <v>315</v>
+      </c>
+      <c r="F3" s="69" t="s">
         <v>316</v>
       </c>
-      <c r="F3" s="69" t="s">
-        <v>317</v>
-      </c>
       <c r="G3" s="69" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H3" s="29"/>
     </row>
@@ -23838,10 +23835,10 @@
         <v>246</v>
       </c>
       <c r="E4" s="67" t="s">
+        <v>315</v>
+      </c>
+      <c r="F4" s="69" t="s">
         <v>316</v>
-      </c>
-      <c r="F4" s="69" t="s">
-        <v>317</v>
       </c>
       <c r="G4" s="69" t="s">
         <v>250</v>
@@ -24854,13 +24851,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="12" customHeight="1">
       <c r="A1" s="29" t="s">
+        <v>301</v>
+      </c>
+      <c r="B1" s="29" t="s">
         <v>302</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="C1" s="29" t="s">
         <v>303</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>304</v>
       </c>
       <c r="D1" s="29" t="s">
         <v>131</v>
@@ -24871,13 +24868,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="29" t="s">
+        <v>313</v>
+      </c>
+      <c r="C2" s="56" t="s">
+        <v>312</v>
+      </c>
+      <c r="D2" s="29" t="s">
         <v>314</v>
-      </c>
-      <c r="C2" s="56" t="s">
-        <v>313</v>
-      </c>
-      <c r="D2" s="29" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="12" customHeight="1">

--- a/360MasterData_AR.xlsx
+++ b/360MasterData_AR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E0A2284-8C03-4B75-A1FE-5E0A8A6DA099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{498EDC38-4D07-47BA-8D5E-B1A9E76CD296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2653" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2653" uniqueCount="369">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -809,9 +809,6 @@
     <t>Answer Media URL</t>
   </si>
   <si>
-    <t>Illus Magnetic Track Light: 5 Common Questions</t>
-  </si>
-  <si>
     <t>Hotspot Icon URL</t>
   </si>
   <si>
@@ -822,12 +819,6 @@
   </si>
   <si>
     <t>Size:30px,Rotate X:68°,Y:0°,Z:0°,Perspective:160°,https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/NAVHST.svg</t>
-  </si>
-  <si>
-    <t>Illus Spot Light: 2 Common Questions</t>
-  </si>
-  <si>
-    <t>Hypnotek Diffucer: 10 Common Questions</t>
   </si>
   <si>
     <t>QNA</t>
@@ -1536,6 +1527,12 @@
   </si>
   <si>
     <t>مرحباً، أنا سارة. الآن وصلنا إلى غرفة النوم الثانية - لنستكشف كيف تُبرز إضاءة Illus، بمؤشر تجسيد اللون العالي الخاص بها، الألوان الحقيقية لمساحتك.</t>
+  </si>
+  <si>
+    <t>مصباح المسار المغناطيسي Illus: 5 أسئلة شائعة</t>
+  </si>
+  <si>
+    <t>موزع هيبنوتيك: ١٠ أسئلة شائعة</t>
   </si>
 </sst>
 </file>
@@ -2755,7 +2752,7 @@
     </row>
     <row r="2" spans="1:28" ht="18.3" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>27</v>
@@ -2767,13 +2764,13 @@
         <v>1</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="F2" s="38" t="s">
         <v>175</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>29</v>
@@ -2782,7 +2779,7 @@
         <v>1</v>
       </c>
       <c r="J2" s="61" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K2" s="61" t="s">
         <v>160</v>
@@ -2818,10 +2815,10 @@
         <v>1</v>
       </c>
       <c r="V2" s="74" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="W2" s="11" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="X2" s="10" t="b">
         <v>1</v>
@@ -2830,18 +2827,18 @@
         <v>1</v>
       </c>
       <c r="Z2" s="67" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="AA2" s="12">
         <v>45750</v>
       </c>
       <c r="AB2" s="71" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:28" ht="20.25" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>27</v>
@@ -2853,13 +2850,13 @@
         <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F3" s="38" t="s">
         <v>166</v>
       </c>
       <c r="G3" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>29</v>
@@ -2904,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="V3" s="74" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="W3" s="11" t="s">
         <v>38</v>
@@ -2916,18 +2913,18 @@
         <v>1</v>
       </c>
       <c r="Z3" s="75" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AA3" s="12">
         <v>45750</v>
       </c>
       <c r="AB3" s="71" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="20.25" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>27</v>
@@ -2939,13 +2936,13 @@
         <v>3</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F4" s="38" t="s">
         <v>165</v>
       </c>
       <c r="G4" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>40</v>
@@ -3003,12 +3000,12 @@
         <v>45750</v>
       </c>
       <c r="AB4" s="71" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="20.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>27</v>
@@ -3020,13 +3017,13 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F5" s="38" t="s">
         <v>163</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>29</v>
@@ -3085,12 +3082,12 @@
         <v>45750</v>
       </c>
       <c r="AB5" s="71" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:28" ht="20.25" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>27</v>
@@ -3102,13 +3099,13 @@
         <v>5</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="F6" s="38" t="s">
         <v>164</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>29</v>
@@ -3167,12 +3164,12 @@
         <v>45750</v>
       </c>
       <c r="AB6" s="71" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="20.25" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>50</v>
@@ -3184,13 +3181,13 @@
         <v>7</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="F7" s="38" t="s">
         <v>167</v>
       </c>
       <c r="G7" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>52</v>
@@ -3199,7 +3196,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="16" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>53</v>
@@ -3249,12 +3246,12 @@
         <v>45750</v>
       </c>
       <c r="AB7" s="71" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="20.25" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>50</v>
@@ -3266,13 +3263,13 @@
         <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F8" s="38" t="s">
         <v>188</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>29</v>
@@ -3281,7 +3278,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="16" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>31</v>
@@ -3333,12 +3330,12 @@
         <v>45750</v>
       </c>
       <c r="AB8" s="70" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="20.25" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>50</v>
@@ -3350,13 +3347,13 @@
         <v>8</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F9" s="38" t="s">
         <v>162</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>29</v>
@@ -3365,7 +3362,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>61</v>
@@ -3417,12 +3414,12 @@
         <v>45750</v>
       </c>
       <c r="AB9" s="70" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="20.25" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>50</v>
@@ -3434,13 +3431,13 @@
         <v>9</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="F10" s="38" t="s">
         <v>208</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>29</v>
@@ -3501,12 +3498,12 @@
         <v>45750</v>
       </c>
       <c r="AB10" s="70" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:28" ht="20.25" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>50</v>
@@ -3518,13 +3515,13 @@
         <v>10</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F11" s="38" t="s">
         <v>207</v>
       </c>
       <c r="G11" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>29</v>
@@ -3583,12 +3580,12 @@
         <v>45750</v>
       </c>
       <c r="AB11" s="70" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:28" ht="20.25" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>50</v>
@@ -3600,13 +3597,13 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>168</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>29</v>
@@ -3667,12 +3664,12 @@
         <v>45750</v>
       </c>
       <c r="AB12" s="70" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="20.25" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>76</v>
@@ -3684,13 +3681,13 @@
         <v>12</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>169</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>29</v>
@@ -3751,12 +3748,12 @@
         <v>45750</v>
       </c>
       <c r="AB13" s="70" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:28" ht="20.25" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>76</v>
@@ -3768,13 +3765,13 @@
         <v>13</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>170</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>29</v>
@@ -3835,12 +3832,12 @@
         <v>45750</v>
       </c>
       <c r="AB14" s="70" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15" spans="1:28" ht="20.25" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>76</v>
@@ -3852,13 +3849,13 @@
         <v>14</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="F15" s="38" t="s">
         <v>171</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>29</v>
@@ -3919,12 +3916,12 @@
         <v>45750</v>
       </c>
       <c r="AB15" s="70" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:28" ht="20.25" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>27</v>
@@ -3936,13 +3933,13 @@
         <v>15</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>172</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>29</v>
@@ -4003,12 +4000,12 @@
         <v>45750</v>
       </c>
       <c r="AB16" s="70" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" spans="1:28" ht="20.25" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>27</v>
@@ -4020,13 +4017,13 @@
         <v>16</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F17" s="38" t="s">
         <v>173</v>
       </c>
       <c r="G17" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>29</v>
@@ -4087,12 +4084,12 @@
         <v>45750</v>
       </c>
       <c r="AB17" s="70" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18" spans="1:28" ht="20.25" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>27</v>
@@ -4104,13 +4101,13 @@
         <v>17</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F18" s="38" t="s">
         <v>174</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>29</v>
@@ -4171,12 +4168,12 @@
         <v>45750</v>
       </c>
       <c r="AB18" s="70" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="1:28" ht="20.25" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>97</v>
@@ -4188,13 +4185,13 @@
         <v>18</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F19" s="38" t="s">
         <v>176</v>
       </c>
       <c r="G19" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>40</v>
@@ -4203,7 +4200,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="16" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="K19" s="5" t="s">
         <v>99</v>
@@ -4255,12 +4252,12 @@
         <v>45750</v>
       </c>
       <c r="AB19" s="72" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:28" ht="20.25" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>97</v>
@@ -4272,13 +4269,13 @@
         <v>19</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F20" s="38" t="s">
         <v>177</v>
       </c>
       <c r="G20" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>29</v>
@@ -4287,7 +4284,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="16" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>31</v>
@@ -4339,12 +4336,12 @@
         <v>45750</v>
       </c>
       <c r="AB20" s="72" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="21" spans="1:28" ht="20.25" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>97</v>
@@ -4356,13 +4353,13 @@
         <v>20</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F21" s="38" t="s">
         <v>178</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>29</v>
@@ -4423,12 +4420,12 @@
         <v>45750</v>
       </c>
       <c r="AB21" s="72" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="22" spans="1:28" ht="20.25" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>97</v>
@@ -4440,13 +4437,13 @@
         <v>21</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F22" s="38" t="s">
         <v>179</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>29</v>
@@ -4507,12 +4504,12 @@
         <v>45750</v>
       </c>
       <c r="AB22" s="72" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="23" spans="1:28" ht="20.25" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>97</v>
@@ -4524,13 +4521,13 @@
         <v>22</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F23" s="38" t="s">
         <v>180</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>29</v>
@@ -4587,18 +4584,18 @@
         <v>1</v>
       </c>
       <c r="Z23" s="75" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="AA23" s="12">
         <v>45750</v>
       </c>
       <c r="AB23" s="37" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="24" spans="1:28" ht="12" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>97</v>
@@ -4610,13 +4607,13 @@
         <v>23</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F24" s="38" t="s">
         <v>194</v>
       </c>
       <c r="G24" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>29</v>
@@ -4677,12 +4674,12 @@
         <v>45750</v>
       </c>
       <c r="AB24" s="37" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="25" spans="1:28" ht="12" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>97</v>
@@ -4694,13 +4691,13 @@
         <v>24</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F25" s="38" t="s">
         <v>189</v>
       </c>
       <c r="G25" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>29</v>
@@ -4748,7 +4745,7 @@
         <v>89</v>
       </c>
       <c r="W25" s="11" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="X25" s="10" t="b">
         <v>1</v>
@@ -4761,12 +4758,12 @@
         <v>45750</v>
       </c>
       <c r="AB25" s="37" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26" spans="1:28" ht="12" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>97</v>
@@ -4778,13 +4775,13 @@
         <v>25</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F26" s="38" t="s">
         <v>181</v>
       </c>
       <c r="G26" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>29</v>
@@ -4832,7 +4829,7 @@
         <v>89</v>
       </c>
       <c r="W26" s="11" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="X26" s="10" t="b">
         <v>1</v>
@@ -4845,12 +4842,12 @@
         <v>45750</v>
       </c>
       <c r="AB26" s="37" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="27" spans="1:28" ht="12" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>97</v>
@@ -4862,13 +4859,13 @@
         <v>26</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F27" s="38" t="s">
         <v>190</v>
       </c>
       <c r="G27" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>29</v>
@@ -4916,7 +4913,7 @@
         <v>89</v>
       </c>
       <c r="W27" s="11" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="X27" s="10" t="b">
         <v>1</v>
@@ -4929,12 +4926,12 @@
         <v>45750</v>
       </c>
       <c r="AB27" s="37" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="28" spans="1:28" ht="12" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>97</v>
@@ -4946,13 +4943,13 @@
         <v>27</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="F28" s="38" t="s">
         <v>191</v>
       </c>
       <c r="G28" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>29</v>
@@ -5013,12 +5010,12 @@
         <v>45750</v>
       </c>
       <c r="AB28" s="37" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29" spans="1:28" ht="12" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>97</v>
@@ -5030,13 +5027,13 @@
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F29" s="38" t="s">
         <v>192</v>
       </c>
       <c r="G29" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>29</v>
@@ -5084,7 +5081,7 @@
         <v>89</v>
       </c>
       <c r="W29" s="11" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="X29" s="10" t="b">
         <v>1</v>
@@ -5097,12 +5094,12 @@
         <v>45750</v>
       </c>
       <c r="AB29" s="37" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="30" spans="1:28" ht="12" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>97</v>
@@ -5114,13 +5111,13 @@
         <v>29</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="F30" s="38" t="s">
         <v>193</v>
       </c>
       <c r="G30" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>29</v>
@@ -5168,7 +5165,7 @@
         <v>89</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="X30" s="10" t="b">
         <v>1</v>
@@ -5181,12 +5178,12 @@
         <v>45750</v>
       </c>
       <c r="AB30" s="37" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="31" spans="1:28" ht="12" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>97</v>
@@ -5198,13 +5195,13 @@
         <v>30</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F31" s="38" t="s">
         <v>195</v>
       </c>
       <c r="G31" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>29</v>
@@ -5252,7 +5249,7 @@
         <v>89</v>
       </c>
       <c r="W31" s="11" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="X31" s="10" t="b">
         <v>1</v>
@@ -5265,12 +5262,12 @@
         <v>45750</v>
       </c>
       <c r="AB31" s="37" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="32" spans="1:28" ht="12" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>97</v>
@@ -5282,13 +5279,13 @@
         <v>31</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F32" s="38" t="s">
         <v>196</v>
       </c>
       <c r="G32" s="38" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>29</v>
@@ -5336,7 +5333,7 @@
         <v>89</v>
       </c>
       <c r="W32" s="11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="X32" s="10" t="b">
         <v>1</v>
@@ -5349,7 +5346,7 @@
         <v>45750</v>
       </c>
       <c r="AB32" s="37" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" spans="4:14" ht="12" customHeight="1">
@@ -10303,7 +10300,7 @@
         <v>158</v>
       </c>
       <c r="O1" s="62" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="P1" s="22"/>
       <c r="Q1" s="22"/>
@@ -10349,7 +10346,7 @@
       </c>
       <c r="N2" s="35"/>
       <c r="O2" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q2"/>
     </row>
@@ -10393,7 +10390,7 @@
       </c>
       <c r="N3" s="35"/>
       <c r="O3" s="56" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="Q3"/>
     </row>
@@ -10437,7 +10434,7 @@
       </c>
       <c r="N4" s="35"/>
       <c r="O4" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q4"/>
     </row>
@@ -10481,7 +10478,7 @@
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="56" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q5"/>
     </row>
@@ -10523,7 +10520,7 @@
       </c>
       <c r="N6" s="7"/>
       <c r="O6" s="56" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q6"/>
     </row>
@@ -10565,7 +10562,7 @@
       </c>
       <c r="N7" s="7"/>
       <c r="O7" s="56" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q7"/>
     </row>
@@ -10607,7 +10604,7 @@
       </c>
       <c r="N8" s="7"/>
       <c r="O8" s="56" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q8"/>
     </row>
@@ -10625,10 +10622,10 @@
         <v>33</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="3" t="s">
@@ -10644,7 +10641,7 @@
         <v>145</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M9" s="3" t="b">
         <v>1</v>
@@ -10666,10 +10663,10 @@
         <v>33</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="3" t="s">
@@ -10685,7 +10682,7 @@
         <v>145</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M10" s="3" t="b">
         <v>1</v>
@@ -10726,7 +10723,7 @@
         <v>145</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="M11" s="3" t="b">
         <v>1</v>
@@ -11113,7 +11110,7 @@
         <v>145</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="M20" s="3" t="b">
         <v>1</v>
@@ -11163,7 +11160,7 @@
       </c>
       <c r="N21" s="35"/>
       <c r="O21" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q21"/>
     </row>
@@ -11207,7 +11204,7 @@
       </c>
       <c r="N22" s="35"/>
       <c r="O22" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q22"/>
     </row>
@@ -11457,7 +11454,7 @@
       </c>
       <c r="N28" s="35"/>
       <c r="O28" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q28"/>
     </row>
@@ -11501,7 +11498,7 @@
       </c>
       <c r="N29" s="35"/>
       <c r="O29" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q29"/>
     </row>
@@ -11750,7 +11747,7 @@
       </c>
       <c r="N35" s="35"/>
       <c r="O35" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q35"/>
     </row>
@@ -11794,7 +11791,7 @@
       </c>
       <c r="N36" s="35"/>
       <c r="O36" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q36"/>
     </row>
@@ -12043,7 +12040,7 @@
       </c>
       <c r="N42" s="35"/>
       <c r="O42" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q42"/>
     </row>
@@ -12087,7 +12084,7 @@
       </c>
       <c r="N43" s="35"/>
       <c r="O43" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q43"/>
     </row>
@@ -12336,7 +12333,7 @@
       </c>
       <c r="N49" s="35"/>
       <c r="O49" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q49"/>
     </row>
@@ -12380,7 +12377,7 @@
       </c>
       <c r="N50" s="35"/>
       <c r="O50" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q50"/>
     </row>
@@ -12629,7 +12626,7 @@
       </c>
       <c r="N56" s="35"/>
       <c r="O56" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q56"/>
     </row>
@@ -12673,7 +12670,7 @@
       </c>
       <c r="N57" s="35"/>
       <c r="O57" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q57"/>
     </row>
@@ -12922,7 +12919,7 @@
       </c>
       <c r="N63" s="35"/>
       <c r="O63" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q63"/>
     </row>
@@ -12966,7 +12963,7 @@
       </c>
       <c r="N64" s="35"/>
       <c r="O64" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q64"/>
     </row>
@@ -13215,7 +13212,7 @@
       </c>
       <c r="N70" s="35"/>
       <c r="O70" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q70"/>
     </row>
@@ -13259,7 +13256,7 @@
       </c>
       <c r="N71" s="35"/>
       <c r="O71" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q71"/>
     </row>
@@ -13508,7 +13505,7 @@
       </c>
       <c r="N77" s="35"/>
       <c r="O77" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q77"/>
     </row>
@@ -13552,7 +13549,7 @@
       </c>
       <c r="N78" s="35"/>
       <c r="O78" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q78"/>
     </row>
@@ -13801,7 +13798,7 @@
       </c>
       <c r="N84" s="35"/>
       <c r="O84" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q84"/>
     </row>
@@ -13845,7 +13842,7 @@
       </c>
       <c r="N85" s="35"/>
       <c r="O85" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q85"/>
     </row>
@@ -14094,7 +14091,7 @@
       </c>
       <c r="N91" s="35"/>
       <c r="O91" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q91"/>
     </row>
@@ -14138,7 +14135,7 @@
       </c>
       <c r="N92" s="35"/>
       <c r="O92" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q92"/>
     </row>
@@ -14387,7 +14384,7 @@
       </c>
       <c r="N98" s="35"/>
       <c r="O98" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q98"/>
     </row>
@@ -14431,7 +14428,7 @@
       </c>
       <c r="N99" s="35"/>
       <c r="O99" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q99"/>
     </row>
@@ -14680,7 +14677,7 @@
       </c>
       <c r="N105" s="35"/>
       <c r="O105" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q105"/>
     </row>
@@ -14724,7 +14721,7 @@
       </c>
       <c r="N106" s="35"/>
       <c r="O106" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q106"/>
     </row>
@@ -14973,7 +14970,7 @@
       </c>
       <c r="N112" s="35"/>
       <c r="O112" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q112"/>
     </row>
@@ -15017,7 +15014,7 @@
       </c>
       <c r="N113" s="35"/>
       <c r="O113" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q113"/>
     </row>
@@ -15266,7 +15263,7 @@
       </c>
       <c r="N119" s="35"/>
       <c r="O119" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q119"/>
     </row>
@@ -15310,7 +15307,7 @@
       </c>
       <c r="N120" s="35"/>
       <c r="O120" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q120"/>
     </row>
@@ -15559,7 +15556,7 @@
       </c>
       <c r="N126" s="35"/>
       <c r="O126" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q126"/>
     </row>
@@ -15603,7 +15600,7 @@
       </c>
       <c r="N127" s="35"/>
       <c r="O127" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q127"/>
     </row>
@@ -15852,7 +15849,7 @@
       </c>
       <c r="N133" s="35"/>
       <c r="O133" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q133"/>
     </row>
@@ -15896,7 +15893,7 @@
       </c>
       <c r="N134" s="35"/>
       <c r="O134" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q134"/>
     </row>
@@ -16145,7 +16142,7 @@
       </c>
       <c r="N140" s="35"/>
       <c r="O140" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q140"/>
     </row>
@@ -16189,7 +16186,7 @@
       </c>
       <c r="N141" s="35"/>
       <c r="O141" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q141"/>
     </row>
@@ -16438,7 +16435,7 @@
       </c>
       <c r="N147" s="35"/>
       <c r="O147" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q147"/>
     </row>
@@ -16482,7 +16479,7 @@
       </c>
       <c r="N148" s="35"/>
       <c r="O148" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q148"/>
     </row>
@@ -16731,7 +16728,7 @@
       </c>
       <c r="N154" s="35"/>
       <c r="O154" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q154"/>
     </row>
@@ -16775,7 +16772,7 @@
       </c>
       <c r="N155" s="35"/>
       <c r="O155" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q155"/>
     </row>
@@ -17024,7 +17021,7 @@
       </c>
       <c r="N161" s="35"/>
       <c r="O161" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q161"/>
     </row>
@@ -17068,7 +17065,7 @@
       </c>
       <c r="N162" s="35"/>
       <c r="O162" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q162"/>
     </row>
@@ -17317,7 +17314,7 @@
       </c>
       <c r="N168" s="35"/>
       <c r="O168" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q168"/>
     </row>
@@ -17361,7 +17358,7 @@
       </c>
       <c r="N169" s="35"/>
       <c r="O169" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q169"/>
     </row>
@@ -17610,7 +17607,7 @@
       </c>
       <c r="N175" s="7"/>
       <c r="O175" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="176" spans="1:17" ht="12" customHeight="1">
@@ -17653,7 +17650,7 @@
       </c>
       <c r="N176" s="7"/>
       <c r="O176" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="177" spans="1:15" ht="12" customHeight="1">
@@ -17901,7 +17898,7 @@
       </c>
       <c r="N182" s="7"/>
       <c r="O182" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="183" spans="1:15" ht="12" customHeight="1">
@@ -17944,7 +17941,7 @@
       </c>
       <c r="N183" s="7"/>
       <c r="O183" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="184" spans="1:15" ht="12" customHeight="1">
@@ -18192,7 +18189,7 @@
       </c>
       <c r="N189" s="7"/>
       <c r="O189" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="190" spans="1:15" ht="12" customHeight="1">
@@ -18235,7 +18232,7 @@
       </c>
       <c r="N190" s="7"/>
       <c r="O190" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="191" spans="1:15" ht="12" customHeight="1">
@@ -18483,7 +18480,7 @@
       </c>
       <c r="N196" s="7"/>
       <c r="O196" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="197" spans="1:15" ht="12" customHeight="1">
@@ -18526,7 +18523,7 @@
       </c>
       <c r="N197" s="7"/>
       <c r="O197" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="198" spans="1:15" ht="12" customHeight="1">
@@ -18774,7 +18771,7 @@
       </c>
       <c r="N203" s="7"/>
       <c r="O203" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="204" spans="1:15" ht="12" customHeight="1">
@@ -18817,7 +18814,7 @@
       </c>
       <c r="N204" s="7"/>
       <c r="O204" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="205" spans="1:15" ht="12" customHeight="1">
@@ -19065,7 +19062,7 @@
       </c>
       <c r="N210" s="7"/>
       <c r="O210" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="211" spans="1:15" ht="12" customHeight="1">
@@ -19108,7 +19105,7 @@
       </c>
       <c r="N211" s="7"/>
       <c r="O211" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="212" spans="1:15" ht="12" customHeight="1">
@@ -19353,7 +19350,7 @@
       </c>
       <c r="N217" s="7"/>
       <c r="O217" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="218" spans="1:15" ht="12" customHeight="1">
@@ -19396,7 +19393,7 @@
       </c>
       <c r="N218" s="7"/>
       <c r="O218" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="219" spans="1:15" ht="12" customHeight="1">
@@ -19639,7 +19636,7 @@
       </c>
       <c r="N224" s="7"/>
       <c r="O224" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="225" spans="1:15" ht="12" customHeight="1">
@@ -19682,7 +19679,7 @@
       </c>
       <c r="N225" s="7"/>
       <c r="O225" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="226" spans="1:15" ht="12" customHeight="1">
@@ -19925,7 +19922,7 @@
       </c>
       <c r="N231" s="7"/>
       <c r="O231" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="232" spans="1:15" ht="12" customHeight="1">
@@ -19968,7 +19965,7 @@
       </c>
       <c r="N232" s="7"/>
       <c r="O232" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="233" spans="1:15" ht="12" customHeight="1">
@@ -23008,16 +23005,16 @@
         <v>210</v>
       </c>
       <c r="C2" s="45" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D2" s="44" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E2" s="41" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F2" s="76" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G2" s="45" t="s">
         <v>146</v>
@@ -23029,10 +23026,10 @@
         <v>160</v>
       </c>
       <c r="J2" s="45" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="K2" s="56" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23043,16 +23040,16 @@
         <v>211</v>
       </c>
       <c r="C3" s="45" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E3" s="40" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F3" s="76" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G3" s="40" t="s">
         <v>147</v>
@@ -23064,10 +23061,10 @@
         <v>31</v>
       </c>
       <c r="J3" s="45" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="K3" s="56" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23078,16 +23075,16 @@
         <v>212</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D4" s="48" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E4" s="40" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F4" s="76" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G4" s="43" t="s">
         <v>146</v>
@@ -23099,10 +23096,10 @@
         <v>31</v>
       </c>
       <c r="J4" s="45" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="K4" s="56" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23113,16 +23110,16 @@
         <v>213</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D5" s="48" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E5" s="40" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F5" s="76" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G5" s="49" t="s">
         <v>146</v>
@@ -23137,7 +23134,7 @@
         <v>44</v>
       </c>
       <c r="K5" s="56" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23148,16 +23145,16 @@
         <v>214</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E6" s="41" t="s">
+        <v>318</v>
+      </c>
+      <c r="F6" s="76" t="s">
         <v>321</v>
-      </c>
-      <c r="F6" s="76" t="s">
-        <v>324</v>
       </c>
       <c r="G6" s="43" t="s">
         <v>146</v>
@@ -23169,10 +23166,10 @@
         <v>31</v>
       </c>
       <c r="J6" s="45" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="K6" s="56" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23183,16 +23180,16 @@
         <v>215</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D7" s="48" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E7" s="40" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F7" s="76" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G7" s="49" t="s">
         <v>146</v>
@@ -23207,7 +23204,7 @@
         <v>44</v>
       </c>
       <c r="K7" s="56" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23218,16 +23215,16 @@
         <v>216</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D8" s="48" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E8" s="41" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="F8" s="76" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G8" s="41" t="s">
         <v>147</v>
@@ -23239,10 +23236,10 @@
         <v>31</v>
       </c>
       <c r="J8" s="41" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="K8" s="56" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23253,14 +23250,14 @@
         <v>217</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D9" s="47"/>
       <c r="E9" s="40" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F9" s="76" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G9" s="49" t="s">
         <v>146</v>
@@ -23272,10 +23269,10 @@
         <v>31</v>
       </c>
       <c r="J9" s="51" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="K9" s="56" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23286,14 +23283,14 @@
         <v>220</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D10" s="44"/>
       <c r="E10" s="41" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F10" s="76" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G10" s="43" t="s">
         <v>146</v>
@@ -23305,10 +23302,10 @@
         <v>31</v>
       </c>
       <c r="J10" s="45" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="K10" s="56" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23319,14 +23316,14 @@
         <v>221</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D11" s="47"/>
       <c r="E11" s="40" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F11" s="76" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G11" s="49" t="s">
         <v>146</v>
@@ -23338,10 +23335,10 @@
         <v>31</v>
       </c>
       <c r="J11" s="40" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="K11" s="56" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23352,14 +23349,14 @@
         <v>222</v>
       </c>
       <c r="C12" s="45" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D12" s="44"/>
       <c r="E12" s="41" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F12" s="76" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G12" s="43" t="s">
         <v>146</v>
@@ -23371,10 +23368,10 @@
         <v>31</v>
       </c>
       <c r="J12" s="51" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="K12" s="56" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23385,14 +23382,14 @@
         <v>223</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D13" s="47"/>
       <c r="E13" s="40" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F13" s="76" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G13" s="40" t="s">
         <v>147</v>
@@ -23404,10 +23401,10 @@
         <v>31</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="K13" s="56" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23418,14 +23415,14 @@
         <v>224</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D14" s="44"/>
       <c r="E14" s="41" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F14" s="76" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G14" s="43" t="s">
         <v>146</v>
@@ -23437,10 +23434,10 @@
         <v>31</v>
       </c>
       <c r="J14" s="51" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="K14" s="56" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23451,14 +23448,14 @@
         <v>225</v>
       </c>
       <c r="C15" s="45" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D15" s="47"/>
       <c r="E15" s="40" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F15" s="76" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G15" s="49" t="s">
         <v>146</v>
@@ -23470,10 +23467,10 @@
         <v>31</v>
       </c>
       <c r="J15" s="45" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="K15" s="56" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23484,14 +23481,14 @@
         <v>226</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D16" s="44"/>
       <c r="E16" s="41" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F16" s="76" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G16" s="43" t="s">
         <v>146</v>
@@ -23503,10 +23500,10 @@
         <v>31</v>
       </c>
       <c r="J16" s="45" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="K16" s="56" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23517,16 +23514,16 @@
         <v>227</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D17" s="47" t="s">
         <v>149</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F17" s="76" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G17" s="49" t="s">
         <v>146</v>
@@ -23538,10 +23535,10 @@
         <v>31</v>
       </c>
       <c r="J17" s="45" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="K17" s="56" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23552,16 +23549,16 @@
         <v>228</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D18" s="44" t="s">
         <v>150</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F18" s="76" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G18" s="41" t="s">
         <v>147</v>
@@ -23576,7 +23573,7 @@
         <v>44</v>
       </c>
       <c r="K18" s="56" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23587,14 +23584,14 @@
         <v>229</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D19" s="47"/>
       <c r="E19" s="40" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F19" s="76" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G19" s="49" t="s">
         <v>146</v>
@@ -23606,10 +23603,10 @@
         <v>31</v>
       </c>
       <c r="J19" s="45" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="K19" s="56" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23620,14 +23617,14 @@
         <v>230</v>
       </c>
       <c r="C20" s="45" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D20" s="44"/>
       <c r="E20" s="41" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F20" s="76" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G20" s="43" t="s">
         <v>146</v>
@@ -23639,10 +23636,10 @@
         <v>31</v>
       </c>
       <c r="J20" s="45" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="K20" s="56" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23653,16 +23650,16 @@
         <v>231</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D21" s="47" t="s">
         <v>148</v>
       </c>
       <c r="E21" s="40" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F21" s="76" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G21" s="49" t="s">
         <v>146</v>
@@ -23674,7 +23671,7 @@
         <v>31</v>
       </c>
       <c r="J21" s="45" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="K21" s="56" t="s">
         <v>233</v>
@@ -23756,7 +23753,7 @@
         <v>121</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D1" s="60" t="s">
         <v>130</v>
@@ -23765,7 +23762,7 @@
         <v>238</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G1" s="28" t="s">
         <v>239</v>
@@ -23777,22 +23774,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="66" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C2" s="68" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D2" s="67" t="s">
-        <v>240</v>
+        <v>367</v>
       </c>
       <c r="E2" s="67" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F2" s="69" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G2" s="69" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="H2" s="63"/>
       <c r="I2" s="64"/>
@@ -23802,22 +23799,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="66" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C3" s="68" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D3" s="67" t="s">
-        <v>245</v>
+        <v>367</v>
       </c>
       <c r="E3" s="67" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F3" s="69" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G3" s="69" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H3" s="29"/>
     </row>
@@ -23826,22 +23823,22 @@
         <v>1</v>
       </c>
       <c r="B4" s="66" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C4" s="68" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D4" s="67" t="s">
-        <v>246</v>
+        <v>368</v>
       </c>
       <c r="E4" s="67" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F4" s="69" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G4" s="69" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="12" customHeight="1"/>
@@ -24844,20 +24841,20 @@
   <cols>
     <col min="1" max="1" width="8.609375" customWidth="1"/>
     <col min="2" max="2" width="33.609375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.44140625" customWidth="1"/>
+    <col min="3" max="3" width="67.609375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="76.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="24" width="8.609375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="12" customHeight="1">
       <c r="A1" s="29" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D1" s="29" t="s">
         <v>131</v>
@@ -24868,13 +24865,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="12" customHeight="1">
@@ -25921,11 +25918,8 @@
     <row r="999" ht="12" customHeight="1"/>
     <row r="1000" ht="12" customHeight="1"/>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{67D04ED0-1A53-4962-BC65-F635AE8E8C5D}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId2"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
